--- a/fixtures/demo-dues-ledger.xlsx
+++ b/fixtures/demo-dues-ledger.xlsx
@@ -96,7 +96,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,16 +107,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFB3261E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAE1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -121,12 +152,101 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,24 +541,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -448,14 +575,14 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>750</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <f>VLOOKUP(B2,Rates!A1:B3,2,FALSE)</f>
         <v>750</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <f>E2-D2</f>
         <v>0</v>
       </c>
@@ -475,8 +602,9 @@
         <f>TEXT(E2,"$#,##0.00")</f>
         <v>$750.00</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -486,14 +614,14 @@
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <f>VLOOKUP(B3,Rates!A1:B3,2,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <f>E3-D3</f>
         <v>120</v>
       </c>
@@ -513,8 +641,9 @@
         <f>TEXT(E3,"$#,##0.00")</f>
         <v>$120.00</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -524,14 +653,14 @@
       <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>150</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <f>VLOOKUP(B4,Rates!A1:B3,2,FALSE)</f>
         <v>300</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <f>E4-D4</f>
         <v>150</v>
       </c>
@@ -551,8 +680,9 @@
         <f>TEXT(E4,"$#,##0.00")</f>
         <v>$300.00</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -562,14 +692,14 @@
       <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>750</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <f>VLOOKUP(B5,Rates!A1:B3,2,FALSE)</f>
         <v>750</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <f>E5-D5</f>
         <v>0</v>
       </c>
@@ -589,8 +719,9 @@
         <f>TEXT(E5,"$#,##0.00")</f>
         <v>$750.00</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -600,14 +731,14 @@
       <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
         <v>120</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <f>VLOOKUP(B6,Rates!A1:B3,2,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="3">
         <f>E6-D6</f>
         <v>0</v>
       </c>
@@ -627,75 +758,76 @@
         <f>TEXT(E6,"$#,##0.00")</f>
         <v>$120.00</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
+      <c r="K6" s="2"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <f>SUM(E2:E6)</f>
         <v>2040</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
+    <row r="10" spans="1:11">
+      <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <f>SUM(F2:F6)</f>
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
+    <row r="11" spans="1:11">
+      <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <f>COUNTIF(G2:G6,"unpaid")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
+    <row r="12" spans="1:11">
+      <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <f>SUMIF(B2:B6,"pro",E2:E6)</f>
         <v>1500</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
+    <row r="13" spans="1:11">
+      <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <f>AVERAGE(E2:E6)</f>
         <v>408</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
+    <row r="14" spans="1:11">
+      <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <f>COUNTIF(I2:I6,"&lt;2022")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
+    <row r="15" spans="1:11">
+      <c r="A15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <f>MAX(LEN(A2),LEN(A3),LEN(A4),LEN(A5),LEN(A6))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
+    <row r="16" spans="1:11">
+      <c r="A16" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B16" t="e">
+      <c r="B16" s="9" t="e">
         <f>VLOOKUP("gold",Rates!A1:B3,2,FALSE)</f>
         <v>#N/A</v>
       </c>
@@ -711,26 +843,26 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="10">
         <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="10">
         <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="10">
         <v>750</v>
       </c>
     </row>

--- a/fixtures/demo-dues-ledger.xlsx
+++ b/fixtures/demo-dues-ledger.xlsx
@@ -541,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -579,7 +579,7 @@
         <v>750</v>
       </c>
       <c r="E2" s="3">
-        <f>VLOOKUP(B2,Rates!A1:B3,2,FALSE)</f>
+        <f>VLOOKUP(B2,Rates!$A$1:$B$3,2,FALSE)</f>
         <v>750</v>
       </c>
       <c r="F2" s="3">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3">
-        <f>VLOOKUP(B3,Rates!A1:B3,2,FALSE)</f>
+        <f>VLOOKUP(B3,Rates!$A$1:$B$3,2,FALSE)</f>
         <v>120</v>
       </c>
       <c r="F3" s="3">
@@ -657,7 +657,7 @@
         <v>150</v>
       </c>
       <c r="E4" s="3">
-        <f>VLOOKUP(B4,Rates!A1:B3,2,FALSE)</f>
+        <f>VLOOKUP(B4,Rates!$A$1:$B$3,2,FALSE)</f>
         <v>300</v>
       </c>
       <c r="F4" s="3">
@@ -696,7 +696,7 @@
         <v>750</v>
       </c>
       <c r="E5" s="3">
-        <f>VLOOKUP(B5,Rates!A1:B3,2,FALSE)</f>
+        <f>VLOOKUP(B5,Rates!$A$1:$B$3,2,FALSE)</f>
         <v>750</v>
       </c>
       <c r="F5" s="3">
@@ -735,7 +735,7 @@
         <v>120</v>
       </c>
       <c r="E6" s="3">
-        <f>VLOOKUP(B6,Rates!A1:B3,2,FALSE)</f>
+        <f>VLOOKUP(B6,Rates!$A$1:$B$3,2,FALSE)</f>
         <v>120</v>
       </c>
       <c r="F6" s="3">
@@ -760,75 +760,75 @@
       </c>
       <c r="K6" s="2"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="4" t="s">
+    <row r="22" spans="1:2">
+      <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="5">
-        <f>SUM(E2:E6)</f>
+      <c r="B22" s="5">
+        <f>SUM(E2:E20)</f>
         <v>2040</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="6" t="s">
+    <row r="23" spans="1:2">
+      <c r="A23" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(F2:F6)</f>
+      <c r="B23" s="7">
+        <f>SUM(F2:F20)</f>
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="6" t="s">
+    <row r="24" spans="1:2">
+      <c r="A24" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="7">
-        <f>COUNTIF(G2:G6,"unpaid")</f>
+      <c r="B24" s="7">
+        <f>COUNTIF(G2:G20,"unpaid")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="6" t="s">
+    <row r="25" spans="1:2">
+      <c r="A25" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="7">
-        <f>SUMIF(B2:B6,"pro",E2:E6)</f>
+      <c r="B25" s="7">
+        <f>SUMIF(B2:B20,"pro",E2:E20)</f>
         <v>1500</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="6" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="7">
-        <f>AVERAGE(E2:E6)</f>
+      <c r="B26" s="7">
+        <f>AVERAGE(E2:E20)</f>
         <v>408</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="6" t="s">
+    <row r="27" spans="1:2">
+      <c r="A27" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="7">
-        <f>COUNTIF(I2:I6,"&lt;2022")</f>
+      <c r="B27" s="7">
+        <f>COUNTIF(I2:I20,"&lt;2022")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="6" t="s">
+    <row r="28" spans="1:2">
+      <c r="A28" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B28" s="7">
         <f>MAX(LEN(A2),LEN(A3),LEN(A4),LEN(A5),LEN(A6))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="8" t="s">
+    <row r="29" spans="1:2">
+      <c r="A29" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="9" t="e">
-        <f>VLOOKUP("gold",Rates!A1:B3,2,FALSE)</f>
+      <c r="B29" s="9" t="e">
+        <f>VLOOKUP("gold",Rates!$A$1:$B$3,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>

--- a/fixtures/demo-dues-ledger.xlsx
+++ b/fixtures/demo-dues-ledger.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>member</t>
   </si>
@@ -27,6 +27,24 @@
   </si>
   <si>
     <t>paid</t>
+  </si>
+  <si>
+    <t>owed</t>
+  </si>
+  <si>
+    <t>balance</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>owed (fmt)</t>
   </si>
   <si>
     <t>Ada</t>
@@ -557,23 +575,35 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="2"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3">
         <v>750</v>
@@ -606,13 +636,13 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3">
         <v>0</v>
@@ -645,13 +675,13 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3">
         <v>150</v>
@@ -684,13 +714,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3">
         <v>750</v>
@@ -723,13 +753,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D6" s="3">
         <v>120</v>
@@ -760,72 +790,142 @@
       </c>
       <c r="K6" s="2"/>
     </row>
-    <row r="22" spans="1:2">
+    <row r="7" spans="1:11">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B22" s="5">
         <f>SUM(E2:E20)</f>
         <v>2040</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:6">
       <c r="A23" s="6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B23" s="7">
         <f>SUM(F2:F20)</f>
         <v>270</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:6">
       <c r="A24" s="6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B24" s="7">
         <f>COUNTIF(G2:G20,"unpaid")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:6">
       <c r="A25" s="6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B25" s="7">
         <f>SUMIF(B2:B20,"pro",E2:E20)</f>
         <v>1500</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:6">
       <c r="A26" s="6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B26" s="7">
         <f>AVERAGE(E2:E20)</f>
         <v>408</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:6">
       <c r="A27" s="6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B27" s="7">
         <f>COUNTIF(I2:I20,"&lt;2022")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:6">
       <c r="A28" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B28" s="7">
         <f>MAX(LEN(A2),LEN(A3),LEN(A4),LEN(A5),LEN(A6))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:6">
       <c r="A29" s="8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B29" s="9" t="e">
         <f>VLOOKUP("gold",Rates!$A$1:$B$3,2,FALSE)</f>
@@ -844,7 +944,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="10" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B1" s="10">
         <v>120</v>
@@ -852,7 +952,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B2" s="10">
         <v>300</v>
@@ -860,7 +960,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="10" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B3" s="10">
         <v>750</v>
